--- a/output/2026-09-20_13_Croazia_Splitsko-dalmatinska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-20_13_Croazia_Splitsko-dalmatinska_Depolverazione_Trattamento_aria.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grossista/distributore (dal 1994) di materiali per installazione ventilazione (ventilatori, tubazioni, griglie e distributori di ventilazione), oltre a materiali per riscaldamento e climatizzazione. Sede: 114. brigade 10, Split. Esistenza e attivita confermate da fonti multiple (sito ufficiale tea-pharia.hr, moja-djelatnost.hr, tvrtke.hr). Non e uno specialista di dust collector industriali puri ma opera come grossista B2B di componentistica di ventilazione (tubazioni, ventilatori, griglie), quindi canale distributivo potenzialmente compatibile da valutare con contatto diretto per l'offerta Dupuy.</t>
+          <t>Grossista/distributore (dal 1994) di materiali per installazione ventilazione (ventilatori, tubazioni, griglie e distributori di ventilazione), oltre a materiali per riscaldamento e climatizzazione. Sede: 114. brigade 10, Split. Esistenza e attivita confermate da fonti multiple (sito ufficiale tea-pharia.hr, moja-djelatnost.hr, tvrtke.hr). Non e uno specialista di dust collector industriali puri ma opera come grossista B2B di componentistica di ventilazione (tubazioni, ventilatori, griglie), quindi canale distributivo potenzialmente compatibile da valutare con contatto diretto per l'offerta Dupuy. [DUPLICATO — vedi anche: 2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -524,7 +524,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Grossista/rivenditore di aspiratori industriali (usisivaci industrijski, linea ELEKTRO maschinen per pulizia chimica ed estrattiva), compressori d'aria, idraulica e pneumatica industriale, con sede a Split. Esistenza confermata tramite pagine indicizzate del sito ufficiale (donit-split.hr/usisivaci.htm, donit-split.hr/kompresori.htm). Telefono ed email non reperiti nelle fonti consultate: lasciati vuoti per non inventare dati. Forte coerenza col target aspirazione/depolverazione industriale.</t>

--- a/output/2026-09-20_13_Croazia_Splitsko-dalmatinska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-20_13_Croazia_Splitsko-dalmatinska_Depolverazione_Trattamento_aria.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
